--- a/artfynd/A 57116-2025 artfynd.xlsx
+++ b/artfynd/A 57116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130247753</v>
       </c>
       <c r="B2" t="n">
-        <v>96069</v>
+        <v>96156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130248165</v>
       </c>
       <c r="B3" t="n">
-        <v>96069</v>
+        <v>96156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130248010</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,103 +963,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>130248324</v>
-      </c>
-      <c r="B5" t="n">
-        <v>97454</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2569</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Stor revmossa</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bazzania trilobata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Livelycke, Livelycke, Boh</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>328915</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6433969</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Kungälv</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Romelanda</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Anna Zeffer</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Anna Zeffer</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57116-2025 artfynd.xlsx
+++ b/artfynd/A 57116-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130247753</v>
+        <v>130248165</v>
       </c>
       <c r="B2" t="n">
         <v>96156</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>328966</v>
+        <v>328915</v>
       </c>
       <c r="R2" t="n">
-        <v>6433993</v>
+        <v>6433969</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130248165</v>
+        <v>130247753</v>
       </c>
       <c r="B3" t="n">
         <v>96156</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328915</v>
+        <v>328966</v>
       </c>
       <c r="R3" t="n">
-        <v>6433969</v>
+        <v>6433993</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>

--- a/artfynd/A 57116-2025 artfynd.xlsx
+++ b/artfynd/A 57116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130247753</v>
       </c>
       <c r="B2" t="n">
-        <v>96156</v>
+        <v>96159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130248165</v>
       </c>
       <c r="B3" t="n">
-        <v>96156</v>
+        <v>96159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57116-2025 artfynd.xlsx
+++ b/artfynd/A 57116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130247753</v>
       </c>
       <c r="B2" t="n">
-        <v>96159</v>
+        <v>96185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130248165</v>
       </c>
       <c r="B3" t="n">
-        <v>96159</v>
+        <v>96185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130248010</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57116-2025 artfynd.xlsx
+++ b/artfynd/A 57116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130247753</v>
+        <v>130248349</v>
       </c>
       <c r="B2" t="n">
-        <v>96185</v>
+        <v>96186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>328966</v>
+        <v>328915</v>
       </c>
       <c r="R2" t="n">
-        <v>6433993</v>
+        <v>6433969</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130248165</v>
+        <v>130247753</v>
       </c>
       <c r="B3" t="n">
-        <v>96185</v>
+        <v>96186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328915</v>
+        <v>328966</v>
       </c>
       <c r="R3" t="n">
-        <v>6433969</v>
+        <v>6433993</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 57116-2025 artfynd.xlsx
+++ b/artfynd/A 57116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130248349</v>
+        <v>130247753</v>
       </c>
       <c r="B2" t="n">
-        <v>96186</v>
+        <v>96187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>328915</v>
+        <v>328966</v>
       </c>
       <c r="R2" t="n">
-        <v>6433969</v>
+        <v>6433993</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130247753</v>
+        <v>130248165</v>
       </c>
       <c r="B3" t="n">
-        <v>96186</v>
+        <v>96187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328966</v>
+        <v>328915</v>
       </c>
       <c r="R3" t="n">
-        <v>6433993</v>
+        <v>6433969</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 57116-2025 artfynd.xlsx
+++ b/artfynd/A 57116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130247753</v>
       </c>
       <c r="B2" t="n">
-        <v>96187</v>
+        <v>96189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130248165</v>
       </c>
       <c r="B3" t="n">
-        <v>96187</v>
+        <v>96189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130248010</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 57116-2025 artfynd.xlsx
+++ b/artfynd/A 57116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130247753</v>
       </c>
       <c r="B2" t="n">
-        <v>96189</v>
+        <v>96193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130248165</v>
       </c>
       <c r="B3" t="n">
-        <v>96189</v>
+        <v>96193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57116-2025 artfynd.xlsx
+++ b/artfynd/A 57116-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130247753</v>
+        <v>130248349</v>
       </c>
       <c r="B2" t="n">
         <v>96193</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>328966</v>
+        <v>328915</v>
       </c>
       <c r="R2" t="n">
-        <v>6433993</v>
+        <v>6433969</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130248165</v>
+        <v>130247753</v>
       </c>
       <c r="B3" t="n">
         <v>96193</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328915</v>
+        <v>328966</v>
       </c>
       <c r="R3" t="n">
-        <v>6433969</v>
+        <v>6433993</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 57116-2025 artfynd.xlsx
+++ b/artfynd/A 57116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130248349</v>
+        <v>130247474</v>
       </c>
       <c r="B2" t="n">
-        <v>96193</v>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>328915</v>
+        <v>328966</v>
       </c>
       <c r="R2" t="n">
-        <v>6433969</v>
+        <v>6433993</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130247753</v>
+        <v>130248165</v>
       </c>
       <c r="B3" t="n">
-        <v>96193</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328966</v>
+        <v>328915</v>
       </c>
       <c r="R3" t="n">
-        <v>6433993</v>
+        <v>6433969</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,11 +872,11 @@
         <v>130248010</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">

--- a/artfynd/A 57116-2025 artfynd.xlsx
+++ b/artfynd/A 57116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130247474</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130248165</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130248010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>